--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -88,13 +88,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>SAMANTHA</t>
+  </si>
+  <si>
     <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>DIEGO OLLIN</t>
+  </si>
+  <si>
+    <t>KARLA</t>
   </si>
 </sst>
 </file>
@@ -1094,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,16 +1162,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920208</v>
+        <v>20330051920307</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1144,6 +1180,98 @@
         <v>13</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920309</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920208</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>18330051920336</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920292</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -94,6 +94,9 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>ZEPEDA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
   </si>
   <si>
     <t>SAMANTHA</t>
+  </si>
+  <si>
+    <t>JOSE ISAIAS</t>
   </si>
   <si>
     <t>NAHOMY</t>
@@ -1130,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1168,10 +1177,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1191,10 +1200,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1208,22 +1217,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920208</v>
+        <v>20330051920374</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1231,22 +1240,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>18330051920336</v>
+        <v>19330051920208</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1254,16 +1263,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920292</v>
+        <v>18330051920336</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -1272,6 +1281,29 @@
         <v>16</v>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920292</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -88,58 +88,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>BERNAL</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>SAMANTHA</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
     <t>DIEGO OLLIN</t>
-  </si>
-  <si>
-    <t>KARLA</t>
   </si>
 </sst>
 </file>
@@ -537,7 +492,7 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -546,13 +501,13 @@
         <v>3</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>91.67</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -615,7 +570,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -624,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -758,19 +713,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H2">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -784,16 +742,19 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>32</v>
       </c>
-      <c r="E3">
-        <v>32</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -807,16 +768,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -827,19 +791,22 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -853,16 +820,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -876,16 +846,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -899,16 +872,19 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>93.75</v>
+      </c>
+      <c r="H8">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -958,22 +934,22 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>91.89</v>
+        <v>97.22</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -990,16 +966,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1016,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>87.88</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1036,7 +1012,7 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -1045,13 +1021,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1068,16 +1044,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1094,16 +1070,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1120,16 +1096,16 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H8">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,139 +1147,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920307</v>
+        <v>18330051920336</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920309</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920374</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920208</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>18330051920336</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920292</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -86,15 +86,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DIEGO OLLIN</t>
   </si>
 </sst>
 </file>
@@ -1115,7 +1106,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1145,29 +1136,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>18330051920336</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
+++ b/docentes/Ángel Martínez Gerson Hermenegildo - Estadisticos 20212.xlsx
@@ -931,16 +931,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -966,7 +966,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -992,7 +992,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1018,7 +1018,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1044,7 +1044,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1070,7 +1070,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1096,7 +1096,7 @@
         <v>93.75</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
